--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -12,8 +12,10 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Tabla_436729" sheetId="5" r:id="rId5"/>
+    <sheet name="Hidden_1_Tabla_436729" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="Hidden_1_Tabla_4367295">Hidden_1_Tabla_436729!$A$1:$A$2</definedName>
     <definedName name="Hidden_17">Hidden_1!$A$1:$A$4</definedName>
     <definedName name="Hidden_211">Hidden_2!$A$1:$A$2</definedName>
     <definedName name="Hidden_331">Hidden_3!$A$1:$A$7</definedName>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="124">
   <si>
     <t>48996</t>
   </si>
@@ -299,58 +301,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>30C0E19A804F502B7A59C3A153F4CF23</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>4822666</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica.</t>
-  </si>
-  <si>
-    <t>12/01/2023</t>
-  </si>
-  <si>
-    <t>10/01/2023</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo por toda vez que no hay una recomendación emitida por la Comisión Estatal de Derechos Humanos.</t>
-  </si>
-  <si>
-    <t>687AE833703F83BA6BDBF9F097BD9D97</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>ver nota</t>
-  </si>
-  <si>
-    <t>4645386</t>
-  </si>
-  <si>
-    <t>Subdirección Juridica</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo por toda vez que no hay una recomendación emitida por la Comisión Estatal de Derechos Humanos</t>
+    <t>subdirección juridica</t>
+  </si>
+  <si>
+    <t>2AA3D40CA1AB5E14405724E8904A16F0</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>8101388</t>
+  </si>
+  <si>
+    <t>26/07/2023</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo, toda vez que no hay una recomendación emitida por la Comisión Nacional de Derechos Humanos; tal como lo establece el mismo reglamento interior de la comision nacional en su capitulo VI.  fracciones I, II, III, IV, V, VI, VII, VIII, IX. en el que hace mencion de las causas de conclusion .</t>
   </si>
   <si>
     <t>Recomendación específica</t>
@@ -401,6 +376,9 @@
     <t>56506</t>
   </si>
   <si>
+    <t>77790</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -411,6 +389,15 @@
   </si>
   <si>
     <t>Segundo apellido</t>
+  </si>
+  <si>
+    <t>Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -806,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM9"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
@@ -847,7 +834,7 @@
     <col min="36" max="36" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="20" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="202" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
@@ -1280,240 +1267,121 @@
     </row>
     <row r="8" spans="1:39" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="C8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AH8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ8" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="AK8" s="3" t="s">
         <v>98</v>
       </c>
       <c r="AL8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM8" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="AM8" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:39" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AH9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ9" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AK9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AL9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AM9" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1527,13 +1395,13 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H200">
       <formula1>Hidden_17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L200">
       <formula1>Hidden_211</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF8:AF201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF8:AF200">
       <formula1>Hidden_331</formula1>
     </dataValidation>
   </dataValidations>
@@ -1548,22 +1416,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1578,12 +1446,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1598,37 +1466,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1638,15 +1506,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -1656,31 +1525,65 @@
       <c r="E1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="F2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+      <formula1>Hidden_1_Tabla_4367295</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
